--- a/XBRL-template-MFRS/Company/02-SOFP-OrderOfLiquidity.xlsx
+++ b/XBRL-template-MFRS/Company/02-SOFP-OrderOfLiquidity.xlsx
@@ -927,8 +927,14 @@
           <t>Assets other than assets held for sale</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
+      <c r="B25" s="30">
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="30">
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24</f>
+        <v/>
+      </c>
       <c r="D25" s="34" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="10">
@@ -937,14 +943,8 @@
           <t>Total non-current assets or disposal groups classified as held for sale or as held for distribution to owners</t>
         </is>
       </c>
-      <c r="B26" s="28">
-        <f>1*B24+1*B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>1*C24+1*C25</f>
-        <v/>
-      </c>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
       <c r="D26" s="33" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="10">
@@ -954,11 +954,11 @@
         </is>
       </c>
       <c r="B27" s="35">
-        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B26</f>
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B26</f>
         <v/>
       </c>
       <c r="C27" s="35">
-        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C26</f>
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C26</f>
         <v/>
       </c>
       <c r="D27" s="36" t="n"/>
@@ -1084,11 +1084,11 @@
         </is>
       </c>
       <c r="B37" s="35">
-        <f>1*B34+1*B35+1*B36</f>
+        <f>1*B30+1*B31+-1*B32+1*B33+1*B35+1*B36</f>
         <v/>
       </c>
       <c r="C37" s="35">
-        <f>1*C34+1*C35+1*C36</f>
+        <f>1*C30+1*C31+-1*C32+1*C33+1*C35+1*C36</f>
         <v/>
       </c>
       <c r="D37" s="36" t="n"/>
@@ -1203,14 +1203,8 @@
           <t>Total contract liabilities</t>
         </is>
       </c>
-      <c r="B46" s="28">
-        <f>1*B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="28">
-        <f>1*C45</f>
-        <v/>
-      </c>
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
       <c r="D46" s="33" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="10">
@@ -1255,8 +1249,14 @@
           <t>Liabilities other than liabilities held for sale</t>
         </is>
       </c>
-      <c r="B50" s="30" t="n"/>
-      <c r="C50" s="30" t="n"/>
+      <c r="B50" s="30">
+        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="30">
+        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49</f>
+        <v/>
+      </c>
       <c r="D50" s="34" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1" s="10">
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="B52" s="28">
-        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51</f>
+        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B51</f>
         <v/>
       </c>
       <c r="C52" s="28">
-        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51</f>
+        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C51</f>
         <v/>
       </c>
       <c r="D52" s="33" t="n"/>
@@ -1518,11 +1518,11 @@
         </is>
       </c>
       <c r="B19" s="35">
-        <f>1*B14+1*B15+1*B16+1*B17+1*B18</f>
+        <f>1*B12+1*B18</f>
         <v/>
       </c>
       <c r="C19" s="35">
-        <f>1*C14+1*C15+1*C16+1*C17+1*C18</f>
+        <f>1*C12+1*C18</f>
         <v/>
       </c>
       <c r="D19" s="36" t="n"/>
@@ -1811,8 +1811,14 @@
           <t>Investment property under construction or development</t>
         </is>
       </c>
-      <c r="B46" s="30" t="n"/>
-      <c r="C46" s="30" t="n"/>
+      <c r="B46" s="30">
+        <f>1*B45</f>
+        <v/>
+      </c>
+      <c r="C46" s="30">
+        <f>1*C45</f>
+        <v/>
+      </c>
       <c r="D46" s="34" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="10">
@@ -1832,11 +1838,11 @@
         </is>
       </c>
       <c r="B48" s="35">
-        <f>1*B41+1*B42+1*B43+1*B45+1*B46+1*B47</f>
+        <f>1*B43+1*B46+1*B47</f>
         <v/>
       </c>
       <c r="C48" s="35">
-        <f>1*C41+1*C42+1*C43+1*C45+1*C46+1*C47</f>
+        <f>1*C43+1*C46+1*C47</f>
         <v/>
       </c>
       <c r="D48" s="36" t="n"/>
@@ -2232,11 +2238,11 @@
         </is>
       </c>
       <c r="B85" s="37">
-        <f>1*B79+1*B80+1*B81+1*B83+1*B84</f>
+        <f>1*B78+1*B79+1*B80+1*B81+1*B82+1*B83+1*B84</f>
         <v/>
       </c>
       <c r="C85" s="37">
-        <f>1*C79+1*C80+1*C81+1*C83+1*C84</f>
+        <f>1*C78+1*C79+1*C80+1*C81+1*C82+1*C83+1*C84</f>
         <v/>
       </c>
       <c r="D85" s="38" t="n"/>
@@ -2328,11 +2334,11 @@
         </is>
       </c>
       <c r="B94" s="37">
-        <f>1*B87+1*B88+1*B89+1*B90+1*B92+1*B93</f>
+        <f>1*B87+1*B88+1*B89+1*B90+1*B91+1*B92+1*B93</f>
         <v/>
       </c>
       <c r="C94" s="37">
-        <f>1*C87+1*C88+1*C89+1*C90+1*C92+1*C93</f>
+        <f>1*C87+1*C88+1*C89+1*C90+1*C91+1*C92+1*C93</f>
         <v/>
       </c>
       <c r="D94" s="38" t="n"/>
@@ -2694,11 +2700,11 @@
         </is>
       </c>
       <c r="B127" s="35">
-        <f>1*B124</f>
+        <f>1*B107+1*B126</f>
         <v/>
       </c>
       <c r="C127" s="35">
-        <f>1*C124</f>
+        <f>1*C107+1*C126</f>
         <v/>
       </c>
       <c r="D127" s="36" t="n"/>
@@ -3267,8 +3273,14 @@
           <t>Non-distributable other reserves</t>
         </is>
       </c>
-      <c r="B179" s="37" t="n"/>
-      <c r="C179" s="37" t="n"/>
+      <c r="B179" s="37">
+        <f>1*B171+1*B172+1*B173+1*B174+1*B175+1*B176+1*B177+1*B178</f>
+        <v/>
+      </c>
+      <c r="C179" s="37">
+        <f>1*C171+1*C172+1*C173+1*C174+1*C175+1*C176+1*C177+1*C178</f>
+        <v/>
+      </c>
       <c r="D179" s="38" t="n"/>
     </row>
     <row r="180" ht="18" customHeight="1" s="10">
@@ -3337,8 +3349,14 @@
           <t>Distributable reserves</t>
         </is>
       </c>
-      <c r="B186" s="30" t="n"/>
-      <c r="C186" s="30" t="n"/>
+      <c r="B186" s="30">
+        <f>1*B181+1*B182+1*B183+1*B184+1*B185</f>
+        <v/>
+      </c>
+      <c r="C186" s="30">
+        <f>1*C181+1*C182+1*C183+1*C184+1*C185</f>
+        <v/>
+      </c>
       <c r="D186" s="34" t="n"/>
     </row>
     <row r="187" ht="18" customHeight="1" s="10">
@@ -3348,11 +3366,11 @@
         </is>
       </c>
       <c r="B187" s="35">
-        <f>1*B171+1*B172+1*B173+1*B174+1*B175+1*B176+1*B177+1*B178+1*B179+1*B181+1*B182+1*B183+1*B184+1*B185+1*B186</f>
+        <f>1*B179+1*B186</f>
         <v/>
       </c>
       <c r="C187" s="35">
-        <f>1*C171+1*C172+1*C173+1*C174+1*C175+1*C176+1*C177+1*C178+1*C179+1*C181+1*C182+1*C183+1*C184+1*C185+1*C186</f>
+        <f>1*C179+1*C186</f>
         <v/>
       </c>
       <c r="D187" s="36" t="n"/>
@@ -4026,11 +4044,11 @@
         </is>
       </c>
       <c r="B250" s="37">
-        <f>1*B244+1*B245+1*B246+1*B247+1*B248+1*B249</f>
+        <f>1*B243+1*B244+1*B245+1*B246+1*B247+1*B248+1*B249</f>
         <v/>
       </c>
       <c r="C250" s="37">
-        <f>1*C244+1*C245+1*C246+1*C247+1*C248+1*C249</f>
+        <f>1*C243+1*C244+1*C245+1*C246+1*C247+1*C248+1*C249</f>
         <v/>
       </c>
       <c r="D250" s="38" t="n"/>
